--- a/tasas-transfi.xlsx
+++ b/tasas-transfi.xlsx
@@ -724,8 +724,8 @@
           <t>Conversión del día 💰
 ✅ Dólar paralelo: 68
 Binance
-✅ 1000 Bs = 1.04 = 3191.65 pesos
-✅ 3191.65 pesos = 1.04 = 975.3 Bs
+✅ 1000 Bs = 1.03 = 3164.95 pesos
+✅ 3164.95 pesos = 1.03 = 952.72 Bs
 Promedio competencia
 ✅ Tasa pesos: 20
 ✅ Tasa Bs: 20
@@ -1142,10 +1142,10 @@
         <v/>
       </c>
       <c r="N10" s="8" t="n">
-        <v>962.509</v>
+        <v>970</v>
       </c>
       <c r="O10" s="8" t="n">
-        <v>3071.99</v>
+        <v>3070</v>
       </c>
     </row>
     <row r="11">
@@ -1178,10 +1178,10 @@
         <v/>
       </c>
       <c r="N12" s="8" t="n">
-        <v>3071.99</v>
+        <v>3085</v>
       </c>
       <c r="O12" s="8" t="n">
-        <v>938.736</v>
+        <v>928.658</v>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1" s="42" thickBot="1">

--- a/tasas-transfi.xlsx
+++ b/tasas-transfi.xlsx
@@ -724,8 +724,8 @@
           <t>Conversión del día 💰
 ✅ Dólar paralelo: 68
 Binance
-✅ 1000 Bs = 1.03 = 3164.95 pesos
-✅ 3164.95 pesos = 1.03 = 952.72 Bs
+✅ 1000 Bs = 1.03 = 3168.33 pesos
+✅ 3168.33 pesos = 1.02 = 957.89 Bs
 Promedio competencia
 ✅ Tasa pesos: 20
 ✅ Tasa Bs: 20
@@ -1142,10 +1142,10 @@
         <v/>
       </c>
       <c r="N10" s="8" t="n">
-        <v>970</v>
+        <v>968.997</v>
       </c>
       <c r="O10" s="8" t="n">
-        <v>3070</v>
+        <v>3070.1</v>
       </c>
     </row>
     <row r="11">
@@ -1178,10 +1178,10 @@
         <v/>
       </c>
       <c r="N12" s="8" t="n">
-        <v>3085</v>
+        <v>3094.44</v>
       </c>
       <c r="O12" s="8" t="n">
-        <v>928.658</v>
+        <v>935.55</v>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1" s="42" thickBot="1">

--- a/tasas-transfi.xlsx
+++ b/tasas-transfi.xlsx
@@ -724,8 +724,8 @@
           <t>Conversión del día 💰
 ✅ Dólar paralelo: 68
 Binance
-✅ 1000 Bs = 1.03 = 3168.33 pesos
-✅ 3168.33 pesos = 1.02 = 957.89 Bs
+✅ 1000 Bs = 1.03 = 3200.69 pesos
+✅ 3200.69 pesos = 1.03 = 963.96 Bs
 Promedio competencia
 ✅ Tasa pesos: 20
 ✅ Tasa Bs: 20
@@ -1142,10 +1142,10 @@
         <v/>
       </c>
       <c r="N10" s="8" t="n">
-        <v>968.997</v>
+        <v>966.98</v>
       </c>
       <c r="O10" s="8" t="n">
-        <v>3070.1</v>
+        <v>3095</v>
       </c>
     </row>
     <row r="11">
@@ -1178,10 +1178,10 @@
         <v/>
       </c>
       <c r="N12" s="8" t="n">
-        <v>3094.44</v>
+        <v>3097.9</v>
       </c>
       <c r="O12" s="8" t="n">
-        <v>935.55</v>
+        <v>933</v>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1" s="42" thickBot="1">

--- a/tasas-transfi.xlsx
+++ b/tasas-transfi.xlsx
@@ -724,8 +724,8 @@
           <t>Conversión del día 💰
 ✅ Dólar paralelo: 68
 Binance
-✅ 1000 Bs = 1.03 = 3200.69 pesos
-✅ 3200.69 pesos = 1.03 = 963.96 Bs
+✅ 1000 Bs = 1.04 = 3212.5 pesos
+✅ 3212.5 pesos = 1.04 = 955.59 Bs
 Promedio competencia
 ✅ Tasa pesos: 20
 ✅ Tasa Bs: 20
@@ -1142,10 +1142,10 @@
         <v/>
       </c>
       <c r="N10" s="8" t="n">
-        <v>966.98</v>
+        <v>960</v>
       </c>
       <c r="O10" s="8" t="n">
-        <v>3095</v>
+        <v>3084</v>
       </c>
     </row>
     <row r="11">
@@ -1178,10 +1178,10 @@
         <v/>
       </c>
       <c r="N12" s="8" t="n">
-        <v>3097.9</v>
+        <v>3092.86</v>
       </c>
       <c r="O12" s="8" t="n">
-        <v>933</v>
+        <v>920</v>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1" s="42" thickBot="1">

--- a/tasas-transfi.xlsx
+++ b/tasas-transfi.xlsx
@@ -724,8 +724,8 @@
           <t>Conversión del día 💰
 ✅ Dólar paralelo: 68
 Binance
-✅ 1000 Bs = 1.04 = 3212.5 pesos
-✅ 3212.5 pesos = 1.04 = 955.59 Bs
+✅ 1000 Bs = 1.04 = 3213.43 pesos
+✅ 3213.43 pesos = 1.04 = 961.27 Bs
 Promedio competencia
 ✅ Tasa pesos: 20
 ✅ Tasa Bs: 20
@@ -1142,10 +1142,10 @@
         <v/>
       </c>
       <c r="N10" s="8" t="n">
-        <v>960</v>
+        <v>961.9</v>
       </c>
       <c r="O10" s="8" t="n">
-        <v>3084</v>
+        <v>3091</v>
       </c>
     </row>
     <row r="11">
@@ -1178,10 +1178,10 @@
         <v/>
       </c>
       <c r="N12" s="8" t="n">
-        <v>3092.86</v>
+        <v>3088.99</v>
       </c>
       <c r="O12" s="8" t="n">
-        <v>920</v>
+        <v>924.04</v>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1" s="42" thickBot="1">

--- a/tasas-transfi.xlsx
+++ b/tasas-transfi.xlsx
@@ -724,8 +724,8 @@
           <t>Conversión del día 💰
 ✅ Dólar paralelo: 68
 Binance
-✅ 1000 Bs = 1.04 = 3213.43 pesos
-✅ 3213.43 pesos = 1.04 = 961.27 Bs
+✅ 1000 Bs = 1.03 = 3193.8 pesos
+✅ 3193.8 pesos = 1.03 = 969.38 Bs
 Promedio competencia
 ✅ Tasa pesos: 20
 ✅ Tasa Bs: 20
@@ -1142,10 +1142,10 @@
         <v/>
       </c>
       <c r="N10" s="8" t="n">
-        <v>961.9</v>
+        <v>967.499</v>
       </c>
       <c r="O10" s="8" t="n">
-        <v>3091</v>
+        <v>3090</v>
       </c>
     </row>
     <row r="11">
@@ -1178,10 +1178,10 @@
         <v/>
       </c>
       <c r="N12" s="8" t="n">
-        <v>3088.99</v>
+        <v>3100.99</v>
       </c>
       <c r="O12" s="8" t="n">
-        <v>924.04</v>
+        <v>941.21</v>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1" s="42" thickBot="1">

--- a/tasas-transfi.xlsx
+++ b/tasas-transfi.xlsx
@@ -724,8 +724,8 @@
           <t>Conversión del día 💰
 ✅ Dólar paralelo: 68
 Binance
-✅ 1000 Bs = 1.03 = 3193.8 pesos
-✅ 3193.8 pesos = 1.03 = 969.38 Bs
+✅ 1000 Bs = 1.03 = 3203.3 pesos
+✅ 3203.3 pesos = 1.03 = 961.5 Bs
 Promedio competencia
 ✅ Tasa pesos: 20
 ✅ Tasa Bs: 20
@@ -1142,10 +1142,10 @@
         <v/>
       </c>
       <c r="N10" s="8" t="n">
-        <v>967.499</v>
+        <v>970</v>
       </c>
       <c r="O10" s="8" t="n">
-        <v>3090</v>
+        <v>3107.2</v>
       </c>
     </row>
     <row r="11">
@@ -1178,10 +1178,10 @@
         <v/>
       </c>
       <c r="N12" s="8" t="n">
-        <v>3100.99</v>
+        <v>3110</v>
       </c>
       <c r="O12" s="8" t="n">
-        <v>941.21</v>
+        <v>933.5</v>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1" s="42" thickBot="1">

--- a/tasas-transfi.xlsx
+++ b/tasas-transfi.xlsx
@@ -724,8 +724,8 @@
           <t>Conversión del día 💰
 ✅ Dólar paralelo: 68
 Binance
-✅ 1000 Bs = 1.03 = 3203.3 pesos
-✅ 3203.3 pesos = 1.03 = 961.5 Bs
+✅ 1000 Bs = 1.03 = 3204.96 pesos
+✅ 3204.96 pesos = 1.03 = 972.31 Bs
 Promedio competencia
 ✅ Tasa pesos: 20
 ✅ Tasa Bs: 20
@@ -1142,10 +1142,10 @@
         <v/>
       </c>
       <c r="N10" s="8" t="n">
-        <v>970</v>
+        <v>967.25</v>
       </c>
       <c r="O10" s="8" t="n">
-        <v>3107.2</v>
+        <v>3100</v>
       </c>
     </row>
     <row r="11">
@@ -1181,7 +1181,7 @@
         <v>3110</v>
       </c>
       <c r="O12" s="8" t="n">
-        <v>933.5</v>
+        <v>943.5</v>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1" s="42" thickBot="1">

--- a/tasas-transfi.xlsx
+++ b/tasas-transfi.xlsx
@@ -724,8 +724,8 @@
           <t>Conversión del día 💰
 ✅ Dólar paralelo: 68
 Binance
-✅ 1000 Bs = 1.03 = 3204.96 pesos
-✅ 3204.96 pesos = 1.03 = 972.31 Bs
+✅ 1000 Bs = 1.03 = 3227.04 pesos
+✅ 3227.04 pesos = 1.03 = 947.02 Bs
 Promedio competencia
 ✅ Tasa pesos: 20
 ✅ Tasa Bs: 20
@@ -1142,10 +1142,10 @@
         <v/>
       </c>
       <c r="N10" s="8" t="n">
-        <v>967.25</v>
+        <v>969</v>
       </c>
       <c r="O10" s="8" t="n">
-        <v>3100</v>
+        <v>3127</v>
       </c>
     </row>
     <row r="11">
@@ -1178,10 +1178,10 @@
         <v/>
       </c>
       <c r="N12" s="8" t="n">
-        <v>3110</v>
+        <v>3134.98</v>
       </c>
       <c r="O12" s="8" t="n">
-        <v>943.5</v>
+        <v>920</v>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1" s="42" thickBot="1">

--- a/tasas-transfi.xlsx
+++ b/tasas-transfi.xlsx
@@ -724,8 +724,8 @@
           <t>Conversión del día 💰
 ✅ Dólar paralelo: 68
 Binance
-✅ 1000 Bs = 1.03 = 3227.04 pesos
-✅ 3227.04 pesos = 1.03 = 947.02 Bs
+✅ 1000 Bs = 1.04 = 3246.89 pesos
+✅ 3246.89 pesos = 1.03 = 960.04 Bs
 Promedio competencia
 ✅ Tasa pesos: 20
 ✅ Tasa Bs: 20
@@ -1142,10 +1142,10 @@
         <v/>
       </c>
       <c r="N10" s="8" t="n">
-        <v>969</v>
+        <v>964</v>
       </c>
       <c r="O10" s="8" t="n">
-        <v>3127</v>
+        <v>3130</v>
       </c>
     </row>
     <row r="11">
@@ -1178,10 +1178,10 @@
         <v/>
       </c>
       <c r="N12" s="8" t="n">
-        <v>3134.98</v>
+        <v>3139.99</v>
       </c>
       <c r="O12" s="8" t="n">
-        <v>920</v>
+        <v>928.431</v>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1" s="42" thickBot="1">

--- a/tasas-transfi.xlsx
+++ b/tasas-transfi.xlsx
@@ -724,8 +724,8 @@
           <t>Conversión del día 💰
 ✅ Dólar paralelo: 68
 Binance
-✅ 1000 Bs = 1.04 = 3246.89 pesos
-✅ 3246.89 pesos = 1.03 = 960.04 Bs
+✅ 1000 Bs = 1.04 = 3309.7 pesos
+✅ 3309.7 pesos = 1.04 = 952.08 Bs
 Promedio competencia
 ✅ Tasa pesos: 20
 ✅ Tasa Bs: 20
@@ -1142,10 +1142,10 @@
         <v/>
       </c>
       <c r="N10" s="8" t="n">
-        <v>964</v>
+        <v>959</v>
       </c>
       <c r="O10" s="8" t="n">
-        <v>3130</v>
+        <v>3174</v>
       </c>
     </row>
     <row r="11">
@@ -1178,10 +1178,10 @@
         <v/>
       </c>
       <c r="N12" s="8" t="n">
-        <v>3139.99</v>
+        <v>3181.48</v>
       </c>
       <c r="O12" s="8" t="n">
-        <v>928.431</v>
+        <v>915.199</v>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1" s="42" thickBot="1">

--- a/tasas-transfi.xlsx
+++ b/tasas-transfi.xlsx
@@ -724,8 +724,8 @@
           <t>Conversión del día 💰
 ✅ Dólar paralelo: 68
 Binance
-✅ 1000 Bs = 1.04 = 3309.7 pesos
-✅ 3309.7 pesos = 1.04 = 952.08 Bs
+✅ 1000 Bs = 1.04 = 3287.49 pesos
+✅ 3287.49 pesos = 1.04 = 958.56 Bs
 Promedio competencia
 ✅ Tasa pesos: 20
 ✅ Tasa Bs: 20
@@ -1142,10 +1142,10 @@
         <v/>
       </c>
       <c r="N10" s="8" t="n">
-        <v>959</v>
+        <v>959.7</v>
       </c>
       <c r="O10" s="8" t="n">
-        <v>3174</v>
+        <v>3155</v>
       </c>
     </row>
     <row r="11">
@@ -1178,10 +1178,10 @@
         <v/>
       </c>
       <c r="N12" s="8" t="n">
-        <v>3181.48</v>
+        <v>3159.98</v>
       </c>
       <c r="O12" s="8" t="n">
-        <v>915.199</v>
+        <v>921.381</v>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1" s="42" thickBot="1">

--- a/tasas-transfi.xlsx
+++ b/tasas-transfi.xlsx
@@ -724,8 +724,8 @@
           <t>Conversión del día 💰
 ✅ Dólar paralelo: 68
 Binance
-✅ 1000 Bs = 1.04 = 3287.49 pesos
-✅ 3287.49 pesos = 1.04 = 958.56 Bs
+✅ 1000 Bs = 1.04 = 3253.39 pesos
+✅ 3253.39 pesos = 1.03 = 953.54 Bs
 Promedio competencia
 ✅ Tasa pesos: 20
 ✅ Tasa Bs: 20
@@ -1142,10 +1142,10 @@
         <v/>
       </c>
       <c r="N10" s="8" t="n">
-        <v>959.7</v>
+        <v>965</v>
       </c>
       <c r="O10" s="8" t="n">
-        <v>3155</v>
+        <v>3139.52</v>
       </c>
     </row>
     <row r="11">
@@ -1178,10 +1178,10 @@
         <v/>
       </c>
       <c r="N12" s="8" t="n">
-        <v>3159.98</v>
+        <v>3156</v>
       </c>
       <c r="O12" s="8" t="n">
-        <v>921.381</v>
+        <v>925</v>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1" s="42" thickBot="1">

--- a/tasas-transfi.xlsx
+++ b/tasas-transfi.xlsx
@@ -724,8 +724,8 @@
           <t>Conversión del día 💰
 ✅ Dólar paralelo: 68
 Binance
-✅ 1000 Bs = 1.04 = 3253.39 pesos
-✅ 3253.39 pesos = 1.03 = 953.54 Bs
+✅ 1000 Bs = 1.04 = 3278.13 pesos
+✅ 3278.13 pesos = 1.04 = 961.4 Bs
 Promedio competencia
 ✅ Tasa pesos: 20
 ✅ Tasa Bs: 20
@@ -1142,10 +1142,10 @@
         <v/>
       </c>
       <c r="N10" s="8" t="n">
-        <v>965</v>
+        <v>960</v>
       </c>
       <c r="O10" s="8" t="n">
-        <v>3139.52</v>
+        <v>3147</v>
       </c>
     </row>
     <row r="11">
@@ -1178,7 +1178,7 @@
         <v/>
       </c>
       <c r="N12" s="8" t="n">
-        <v>3156</v>
+        <v>3154</v>
       </c>
       <c r="O12" s="8" t="n">
         <v>925</v>

--- a/tasas-transfi.xlsx
+++ b/tasas-transfi.xlsx
@@ -724,8 +724,8 @@
           <t>Conversión del día 💰
 ✅ Dólar paralelo: 68
 Binance
-✅ 1000 Bs = 1.04 = 3278.13 pesos
-✅ 3278.13 pesos = 1.04 = 961.4 Bs
+✅ 1000 Bs = 1.05 = 3301.58 pesos
+✅ 3301.58 pesos = 1.04 = 960.92 Bs
 Promedio competencia
 ✅ Tasa pesos: 20
 ✅ Tasa Bs: 20
@@ -1142,10 +1142,10 @@
         <v/>
       </c>
       <c r="N10" s="8" t="n">
-        <v>960</v>
+        <v>955</v>
       </c>
       <c r="O10" s="8" t="n">
-        <v>3147</v>
+        <v>3153.01</v>
       </c>
     </row>
     <row r="11">
@@ -1178,10 +1178,10 @@
         <v/>
       </c>
       <c r="N12" s="8" t="n">
-        <v>3154</v>
+        <v>3161</v>
       </c>
       <c r="O12" s="8" t="n">
-        <v>925</v>
+        <v>920</v>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1" s="42" thickBot="1">

--- a/tasas-transfi.xlsx
+++ b/tasas-transfi.xlsx
@@ -724,8 +724,8 @@
           <t>Conversión del día 💰
 ✅ Dólar paralelo: 68
 Binance
-✅ 1000 Bs = 1.05 = 3301.58 pesos
-✅ 3301.58 pesos = 1.04 = 960.92 Bs
+✅ 1000 Bs = 1.05 = 3298.17 pesos
+✅ 3298.17 pesos = 1.04 = 966.51 Bs
 Promedio competencia
 ✅ Tasa pesos: 20
 ✅ Tasa Bs: 20
@@ -1142,10 +1142,10 @@
         <v/>
       </c>
       <c r="N10" s="8" t="n">
-        <v>955</v>
+        <v>956</v>
       </c>
       <c r="O10" s="8" t="n">
-        <v>3153.01</v>
+        <v>3153.05</v>
       </c>
     </row>
     <row r="11">
@@ -1178,10 +1178,10 @@
         <v/>
       </c>
       <c r="N12" s="8" t="n">
-        <v>3161</v>
+        <v>3169.99</v>
       </c>
       <c r="O12" s="8" t="n">
-        <v>920</v>
+        <v>928.95</v>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1" s="42" thickBot="1">

--- a/tasas-transfi.xlsx
+++ b/tasas-transfi.xlsx
@@ -724,8 +724,8 @@
           <t>Conversión del día 💰
 ✅ Dólar paralelo: 68
 Binance
-✅ 1000 Bs = 1.05 = 3298.17 pesos
-✅ 3298.17 pesos = 1.04 = 966.51 Bs
+✅ 1000 Bs = 1.04 = 3292.27 pesos
+✅ 3292.27 pesos = 1.03 = 960.84 Bs
 Promedio competencia
 ✅ Tasa pesos: 20
 ✅ Tasa Bs: 20
@@ -1142,10 +1142,10 @@
         <v/>
       </c>
       <c r="N10" s="8" t="n">
-        <v>956</v>
+        <v>965.9</v>
       </c>
       <c r="O10" s="8" t="n">
-        <v>3153.05</v>
+        <v>3180</v>
       </c>
     </row>
     <row r="11">
@@ -1178,7 +1178,7 @@
         <v/>
       </c>
       <c r="N12" s="8" t="n">
-        <v>3169.99</v>
+        <v>3182.99</v>
       </c>
       <c r="O12" s="8" t="n">
         <v>928.95</v>

--- a/tasas-transfi.xlsx
+++ b/tasas-transfi.xlsx
@@ -724,8 +724,8 @@
           <t>Conversión del día 💰
 ✅ Dólar paralelo: 68
 Binance
-✅ 1000 Bs = 1.04 = 3292.27 pesos
-✅ 3292.27 pesos = 1.03 = 960.84 Bs
+✅ 1000 Bs = 1.04 = 3311.68 pesos
+✅ 3311.68 pesos = 1.05 = 952.02 Bs
 Promedio competencia
 ✅ Tasa pesos: 20
 ✅ Tasa Bs: 20
@@ -1142,10 +1142,10 @@
         <v/>
       </c>
       <c r="N10" s="8" t="n">
-        <v>965.9</v>
+        <v>959.99</v>
       </c>
       <c r="O10" s="8" t="n">
-        <v>3180</v>
+        <v>3179.18</v>
       </c>
     </row>
     <row r="11">
@@ -1178,10 +1178,10 @@
         <v/>
       </c>
       <c r="N12" s="8" t="n">
-        <v>3182.99</v>
+        <v>3169</v>
       </c>
       <c r="O12" s="8" t="n">
-        <v>928.95</v>
+        <v>911</v>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1" s="42" thickBot="1">

--- a/tasas-transfi.xlsx
+++ b/tasas-transfi.xlsx
@@ -724,8 +724,8 @@
           <t>Conversión del día 💰
 ✅ Dólar paralelo: 68
 Binance
-✅ 1000 Bs = 1.04 = 3311.68 pesos
-✅ 3311.68 pesos = 1.05 = 952.02 Bs
+✅ 1000 Bs = 1.04 = 3326.08 pesos
+✅ 3326.08 pesos = 1.04 = 957.75 Bs
 Promedio competencia
 ✅ Tasa pesos: 20
 ✅ Tasa Bs: 20
@@ -1145,7 +1145,7 @@
         <v>959.99</v>
       </c>
       <c r="O10" s="8" t="n">
-        <v>3179.18</v>
+        <v>3193</v>
       </c>
     </row>
     <row r="11">
@@ -1178,10 +1178,10 @@
         <v/>
       </c>
       <c r="N12" s="8" t="n">
-        <v>3169</v>
+        <v>3194.99</v>
       </c>
       <c r="O12" s="8" t="n">
-        <v>911</v>
+        <v>920</v>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1" s="42" thickBot="1">

--- a/tasas-transfi.xlsx
+++ b/tasas-transfi.xlsx
@@ -724,8 +724,8 @@
           <t>Conversión del día 💰
 ✅ Dólar paralelo: 68
 Binance
-✅ 1000 Bs = 1.04 = 3326.08 pesos
-✅ 3326.08 pesos = 1.04 = 957.75 Bs
+✅ 1000 Bs = 1.03 = 3273.4 pesos
+✅ 3273.4 pesos = 1.03 = 963.43 Bs
 Promedio competencia
 ✅ Tasa pesos: 20
 ✅ Tasa Bs: 20
@@ -1142,10 +1142,10 @@
         <v/>
       </c>
       <c r="N10" s="8" t="n">
-        <v>959.99</v>
+        <v>970</v>
       </c>
       <c r="O10" s="8" t="n">
-        <v>3193</v>
+        <v>3175.2</v>
       </c>
     </row>
     <row r="11">
@@ -1178,10 +1178,10 @@
         <v/>
       </c>
       <c r="N12" s="8" t="n">
-        <v>3194.99</v>
+        <v>3179.99</v>
       </c>
       <c r="O12" s="8" t="n">
-        <v>920</v>
+        <v>935.9400000000001</v>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1" s="42" thickBot="1">

--- a/tasas-transfi.xlsx
+++ b/tasas-transfi.xlsx
@@ -724,8 +724,8 @@
           <t>Conversión del día 💰
 ✅ Dólar paralelo: 68
 Binance
-✅ 1000 Bs = 1.03 = 3273.4 pesos
-✅ 3273.4 pesos = 1.03 = 963.43 Bs
+✅ 1000 Bs = 1.02 = 3296.5 pesos
+✅ 3296.5 pesos = 1.02 = 953.77 Bs
 Promedio competencia
 ✅ Tasa pesos: 20
 ✅ Tasa Bs: 20
@@ -1142,10 +1142,10 @@
         <v/>
       </c>
       <c r="N10" s="8" t="n">
-        <v>970</v>
+        <v>980</v>
       </c>
       <c r="O10" s="8" t="n">
-        <v>3175.2</v>
+        <v>3230.57</v>
       </c>
     </row>
     <row r="11">
@@ -1178,10 +1178,10 @@
         <v/>
       </c>
       <c r="N12" s="8" t="n">
-        <v>3179.99</v>
+        <v>3238</v>
       </c>
       <c r="O12" s="8" t="n">
-        <v>935.9400000000001</v>
+        <v>936.842</v>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1" s="42" thickBot="1">

--- a/tasas-transfi.xlsx
+++ b/tasas-transfi.xlsx
@@ -724,8 +724,8 @@
           <t>Conversión del día 💰
 ✅ Dólar paralelo: 68
 Binance
-✅ 1000 Bs = 1.02 = 3296.5 pesos
-✅ 3296.5 pesos = 1.02 = 953.77 Bs
+✅ 1000 Bs = 1.02 = 3325.14 pesos
+✅ 3325.14 pesos = 1.02 = 966.01 Bs
 Promedio competencia
 ✅ Tasa pesos: 20
 ✅ Tasa Bs: 20
@@ -1142,10 +1142,10 @@
         <v/>
       </c>
       <c r="N10" s="8" t="n">
-        <v>980</v>
+        <v>976.2</v>
       </c>
       <c r="O10" s="8" t="n">
-        <v>3230.57</v>
+        <v>3246</v>
       </c>
     </row>
     <row r="11">
@@ -1178,10 +1178,10 @@
         <v/>
       </c>
       <c r="N12" s="8" t="n">
-        <v>3238</v>
+        <v>3249.39</v>
       </c>
       <c r="O12" s="8" t="n">
-        <v>936.842</v>
+        <v>944</v>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1" s="42" thickBot="1">

--- a/tasas-transfi.xlsx
+++ b/tasas-transfi.xlsx
@@ -724,8 +724,8 @@
           <t>Conversión del día 💰
 ✅ Dólar paralelo: 68
 Binance
-✅ 1000 Bs = 1.02 = 3325.14 pesos
-✅ 3325.14 pesos = 1.02 = 966.01 Bs
+✅ 1000 Bs = 1.02 = 3383.53 pesos
+✅ 3383.53 pesos = 1.02 = 966.68 Bs
 Promedio competencia
 ✅ Tasa pesos: 20
 ✅ Tasa Bs: 20
@@ -1145,7 +1145,7 @@
         <v>976.2</v>
       </c>
       <c r="O10" s="8" t="n">
-        <v>3246</v>
+        <v>3303</v>
       </c>
     </row>
     <row r="11">
@@ -1178,10 +1178,10 @@
         <v/>
       </c>
       <c r="N12" s="8" t="n">
-        <v>3249.39</v>
+        <v>3311.5</v>
       </c>
       <c r="O12" s="8" t="n">
-        <v>944</v>
+        <v>946.1</v>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1" s="42" thickBot="1">

--- a/tasas-transfi.xlsx
+++ b/tasas-transfi.xlsx
@@ -724,8 +724,8 @@
           <t>Conversión del día 💰
 ✅ Dólar paralelo: 68
 Binance
-✅ 1000 Bs = 1.02 = 3383.53 pesos
-✅ 3383.53 pesos = 1.02 = 966.68 Bs
+✅ 1000 Bs = 1.02 = 3389.57 pesos
+✅ 3389.57 pesos = 1.03 = 970.04 Bs
 Promedio competencia
 ✅ Tasa pesos: 20
 ✅ Tasa Bs: 20
@@ -1142,10 +1142,10 @@
         <v/>
       </c>
       <c r="N10" s="8" t="n">
-        <v>976.2</v>
+        <v>978</v>
       </c>
       <c r="O10" s="8" t="n">
-        <v>3303</v>
+        <v>3315</v>
       </c>
     </row>
     <row r="11">
@@ -1178,10 +1178,10 @@
         <v/>
       </c>
       <c r="N12" s="8" t="n">
-        <v>3311.5</v>
+        <v>3298.98</v>
       </c>
       <c r="O12" s="8" t="n">
-        <v>946.1</v>
+        <v>944.11</v>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1" s="42" thickBot="1">

--- a/tasas-transfi.xlsx
+++ b/tasas-transfi.xlsx
@@ -724,8 +724,8 @@
           <t>Conversión del día 💰
 ✅ Dólar paralelo: 68
 Binance
-✅ 1000 Bs = 1.02 = 3389.57 pesos
-✅ 3389.57 pesos = 1.03 = 970.04 Bs
+✅ 1000 Bs = 1.02 = 3345.29 pesos
+✅ 3345.29 pesos = 1.02 = 957.99 Bs
 Promedio competencia
 ✅ Tasa pesos: 20
 ✅ Tasa Bs: 20
@@ -1142,10 +1142,10 @@
         <v/>
       </c>
       <c r="N10" s="8" t="n">
-        <v>978</v>
+        <v>975.999</v>
       </c>
       <c r="O10" s="8" t="n">
-        <v>3315</v>
+        <v>3265</v>
       </c>
     </row>
     <row r="11">
@@ -1178,10 +1178,10 @@
         <v/>
       </c>
       <c r="N12" s="8" t="n">
-        <v>3298.98</v>
+        <v>3265</v>
       </c>
       <c r="O12" s="8" t="n">
-        <v>944.11</v>
+        <v>935</v>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1" s="42" thickBot="1">

--- a/tasas-transfi.xlsx
+++ b/tasas-transfi.xlsx
@@ -724,8 +724,8 @@
           <t>Conversión del día 💰
 ✅ Dólar paralelo: 68
 Binance
-✅ 1000 Bs = 1.02 = 3345.29 pesos
-✅ 3345.29 pesos = 1.02 = 957.99 Bs
+✅ 1000 Bs = 1.02 = 3343.42 pesos
+✅ 3343.42 pesos = 1.02 = 961.11 Bs
 Promedio competencia
 ✅ Tasa pesos: 20
 ✅ Tasa Bs: 20
@@ -1142,10 +1142,10 @@
         <v/>
       </c>
       <c r="N10" s="8" t="n">
-        <v>975.999</v>
+        <v>976.777</v>
       </c>
       <c r="O10" s="8" t="n">
-        <v>3265</v>
+        <v>3265.78</v>
       </c>
     </row>
     <row r="11">
@@ -1178,10 +1178,10 @@
         <v/>
       </c>
       <c r="N12" s="8" t="n">
-        <v>3265</v>
+        <v>3274.85</v>
       </c>
       <c r="O12" s="8" t="n">
-        <v>935</v>
+        <v>941.4</v>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1" s="42" thickBot="1">

--- a/tasas-transfi.xlsx
+++ b/tasas-transfi.xlsx
@@ -724,8 +724,8 @@
           <t>Conversión del día 💰
 ✅ Dólar paralelo: 68
 Binance
-✅ 1000 Bs = 1.02 = 3343.42 pesos
-✅ 3343.42 pesos = 1.02 = 961.11 Bs
+✅ 1000 Bs = 1.02 = 3340.17 pesos
+✅ 3340.17 pesos = 1.02 = 973.36 Bs
 Promedio competencia
 ✅ Tasa pesos: 20
 ✅ Tasa Bs: 20
@@ -1142,10 +1142,10 @@
         <v/>
       </c>
       <c r="N10" s="8" t="n">
-        <v>976.777</v>
+        <v>976</v>
       </c>
       <c r="O10" s="8" t="n">
-        <v>3265.78</v>
+        <v>3260.01</v>
       </c>
     </row>
     <row r="11">
@@ -1178,10 +1178,10 @@
         <v/>
       </c>
       <c r="N12" s="8" t="n">
-        <v>3274.85</v>
+        <v>3260</v>
       </c>
       <c r="O12" s="8" t="n">
-        <v>941.4</v>
+        <v>950</v>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1" s="42" thickBot="1">

--- a/tasas-transfi.xlsx
+++ b/tasas-transfi.xlsx
@@ -724,8 +724,8 @@
           <t>Conversión del día 💰
 ✅ Dólar paralelo: 68
 Binance
-✅ 1000 Bs = 1.02 = 3340.17 pesos
-✅ 3340.17 pesos = 1.02 = 973.36 Bs
+✅ 1000 Bs = 1.03 = 3341.91 pesos
+✅ 3341.91 pesos = 1.03 = 966.19 Bs
 Promedio competencia
 ✅ Tasa pesos: 20
 ✅ Tasa Bs: 20
@@ -1142,10 +1142,10 @@
         <v/>
       </c>
       <c r="N10" s="8" t="n">
-        <v>976</v>
+        <v>974</v>
       </c>
       <c r="O10" s="8" t="n">
-        <v>3260.01</v>
+        <v>3255.02</v>
       </c>
     </row>
     <row r="11">
@@ -1178,10 +1178,10 @@
         <v/>
       </c>
       <c r="N12" s="8" t="n">
-        <v>3260</v>
+        <v>3258.25</v>
       </c>
       <c r="O12" s="8" t="n">
-        <v>950</v>
+        <v>942</v>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1" s="42" thickBot="1">

--- a/tasas-transfi.xlsx
+++ b/tasas-transfi.xlsx
@@ -724,8 +724,8 @@
           <t>Conversión del día 💰
 ✅ Dólar paralelo: 68
 Binance
-✅ 1000 Bs = 1.03 = 3341.91 pesos
-✅ 3341.91 pesos = 1.03 = 966.19 Bs
+✅ 1000 Bs = 1.03 = 3352.06 pesos
+✅ 3352.06 pesos = 1.02 = 942.8 Bs
 Promedio competencia
 ✅ Tasa pesos: 20
 ✅ Tasa Bs: 20
@@ -1142,10 +1142,10 @@
         <v/>
       </c>
       <c r="N10" s="8" t="n">
-        <v>974</v>
+        <v>971.35</v>
       </c>
       <c r="O10" s="8" t="n">
-        <v>3255.02</v>
+        <v>3256.02</v>
       </c>
     </row>
     <row r="11">
@@ -1178,10 +1178,10 @@
         <v/>
       </c>
       <c r="N12" s="8" t="n">
-        <v>3258.25</v>
+        <v>3271</v>
       </c>
       <c r="O12" s="8" t="n">
-        <v>942</v>
+        <v>920</v>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1" s="42" thickBot="1">

--- a/tasas-transfi.xlsx
+++ b/tasas-transfi.xlsx
@@ -724,8 +724,8 @@
           <t>Conversión del día 💰
 ✅ Dólar paralelo: 68
 Binance
-✅ 1000 Bs = 1.03 = 3352.06 pesos
-✅ 3352.06 pesos = 1.02 = 942.8 Bs
+✅ 1000 Bs = 1.02 = 3338.11 pesos
+✅ 3338.11 pesos = 1.02 = 947.06 Bs
 Promedio competencia
 ✅ Tasa pesos: 20
 ✅ Tasa Bs: 20
@@ -1142,10 +1142,10 @@
         <v/>
       </c>
       <c r="N10" s="8" t="n">
-        <v>971.35</v>
+        <v>976</v>
       </c>
       <c r="O10" s="8" t="n">
-        <v>3256.02</v>
+        <v>3258</v>
       </c>
     </row>
     <row r="11">
@@ -1178,10 +1178,10 @@
         <v/>
       </c>
       <c r="N12" s="8" t="n">
-        <v>3271</v>
+        <v>3278</v>
       </c>
       <c r="O12" s="8" t="n">
-        <v>920</v>
+        <v>930</v>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1" s="42" thickBot="1">

--- a/tasas-transfi.xlsx
+++ b/tasas-transfi.xlsx
@@ -724,8 +724,8 @@
           <t>Conversión del día 💰
 ✅ Dólar paralelo: 68
 Binance
-✅ 1000 Bs = 1.02 = 3338.11 pesos
-✅ 3338.11 pesos = 1.02 = 947.06 Bs
+✅ 1000 Bs = 1.03 = 3409.65 pesos
+✅ 3409.65 pesos = 1.02 = 954.58 Bs
 Promedio competencia
 ✅ Tasa pesos: 20
 ✅ Tasa Bs: 20
@@ -1142,10 +1142,10 @@
         <v/>
       </c>
       <c r="N10" s="8" t="n">
-        <v>976</v>
+        <v>974</v>
       </c>
       <c r="O10" s="8" t="n">
-        <v>3258</v>
+        <v>3321</v>
       </c>
     </row>
     <row r="11">
@@ -1178,10 +1178,10 @@
         <v/>
       </c>
       <c r="N12" s="8" t="n">
-        <v>3278</v>
+        <v>3328.99</v>
       </c>
       <c r="O12" s="8" t="n">
-        <v>930</v>
+        <v>932</v>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1" s="42" thickBot="1">

--- a/tasas-transfi.xlsx
+++ b/tasas-transfi.xlsx
@@ -724,8 +724,8 @@
           <t>Conversión del día 💰
 ✅ Dólar paralelo: 68
 Binance
-✅ 1000 Bs = 1.03 = 3409.65 pesos
-✅ 3409.65 pesos = 1.02 = 954.58 Bs
+✅ 1000 Bs = 1.02 = 3400.61 pesos
+✅ 3400.61 pesos = 1.02 = 951.76 Bs
 Promedio competencia
 ✅ Tasa pesos: 20
 ✅ Tasa Bs: 20
@@ -1142,10 +1142,10 @@
         <v/>
       </c>
       <c r="N10" s="8" t="n">
-        <v>974</v>
+        <v>976</v>
       </c>
       <c r="O10" s="8" t="n">
-        <v>3321</v>
+        <v>3319</v>
       </c>
     </row>
     <row r="11">
@@ -1178,7 +1178,7 @@
         <v/>
       </c>
       <c r="N12" s="8" t="n">
-        <v>3328.99</v>
+        <v>3330</v>
       </c>
       <c r="O12" s="8" t="n">
         <v>932</v>

--- a/tasas-transfi.xlsx
+++ b/tasas-transfi.xlsx
@@ -724,8 +724,8 @@
           <t>Conversión del día 💰
 ✅ Dólar paralelo: 68
 Binance
-✅ 1000 Bs = 1.02 = 3400.61 pesos
-✅ 3400.61 pesos = 1.02 = 951.76 Bs
+✅ 1000 Bs = 1.04 = 3428.86 pesos
+✅ 3428.86 pesos = 1.03 = 950.17 Bs
 Promedio competencia
 ✅ Tasa pesos: 20
 ✅ Tasa Bs: 20
@@ -1142,10 +1142,10 @@
         <v/>
       </c>
       <c r="N10" s="8" t="n">
-        <v>976</v>
+        <v>965</v>
       </c>
       <c r="O10" s="8" t="n">
-        <v>3319</v>
+        <v>3308.85</v>
       </c>
     </row>
     <row r="11">
@@ -1178,10 +1178,10 @@
         <v/>
       </c>
       <c r="N12" s="8" t="n">
-        <v>3330</v>
+        <v>3320</v>
       </c>
       <c r="O12" s="8" t="n">
-        <v>932</v>
+        <v>920</v>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1" s="42" thickBot="1">

--- a/tasas-transfi.xlsx
+++ b/tasas-transfi.xlsx
@@ -724,8 +724,8 @@
           <t>Conversión del día 💰
 ✅ Dólar paralelo: 68
 Binance
-✅ 1000 Bs = 1.04 = 3428.86 pesos
-✅ 3428.86 pesos = 1.03 = 950.17 Bs
+✅ 1000 Bs = 1.03 = 3415.46 pesos
+✅ 3415.46 pesos = 1.03 = 955.18 Bs
 Promedio competencia
 ✅ Tasa pesos: 20
 ✅ Tasa Bs: 20
@@ -1142,10 +1142,10 @@
         <v/>
       </c>
       <c r="N10" s="8" t="n">
-        <v>965</v>
+        <v>970</v>
       </c>
       <c r="O10" s="8" t="n">
-        <v>3308.85</v>
+        <v>3313</v>
       </c>
     </row>
     <row r="11">
@@ -1178,10 +1178,10 @@
         <v/>
       </c>
       <c r="N12" s="8" t="n">
-        <v>3320</v>
+        <v>3314.31</v>
       </c>
       <c r="O12" s="8" t="n">
-        <v>920</v>
+        <v>926.888</v>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1" s="42" thickBot="1">

--- a/tasas-transfi.xlsx
+++ b/tasas-transfi.xlsx
@@ -724,8 +724,8 @@
           <t>Conversión del día 💰
 ✅ Dólar paralelo: 68
 Binance
-✅ 1000 Bs = 1.03 = 3415.46 pesos
-✅ 3415.46 pesos = 1.03 = 955.18 Bs
+✅ 1000 Bs = 1.03 = 3400.83 pesos
+✅ 3400.83 pesos = 1.03 = 950.98 Bs
 Promedio competencia
 ✅ Tasa pesos: 20
 ✅ Tasa Bs: 20
@@ -1142,10 +1142,10 @@
         <v/>
       </c>
       <c r="N10" s="8" t="n">
-        <v>970</v>
+        <v>968</v>
       </c>
       <c r="O10" s="8" t="n">
-        <v>3313</v>
+        <v>3292</v>
       </c>
     </row>
     <row r="11">
@@ -1178,10 +1178,10 @@
         <v/>
       </c>
       <c r="N12" s="8" t="n">
-        <v>3314.31</v>
+        <v>3307.94</v>
       </c>
       <c r="O12" s="8" t="n">
-        <v>926.888</v>
+        <v>925.01</v>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1" s="42" thickBot="1">

--- a/tasas-transfi.xlsx
+++ b/tasas-transfi.xlsx
@@ -724,8 +724,8 @@
           <t>Conversión del día 💰
 ✅ Dólar paralelo: 68
 Binance
-✅ 1000 Bs = 1.03 = 3400.83 pesos
-✅ 3400.83 pesos = 1.03 = 950.98 Bs
+✅ 1000 Bs = 1.03 = 3364.2 pesos
+✅ 3364.2 pesos = 1.03 = 948.24 Bs
 Promedio competencia
 ✅ Tasa pesos: 20
 ✅ Tasa Bs: 20
@@ -1142,10 +1142,10 @@
         <v/>
       </c>
       <c r="N10" s="8" t="n">
-        <v>968</v>
+        <v>972</v>
       </c>
       <c r="O10" s="8" t="n">
-        <v>3292</v>
+        <v>3270</v>
       </c>
     </row>
     <row r="11">
@@ -1178,10 +1178,10 @@
         <v/>
       </c>
       <c r="N12" s="8" t="n">
-        <v>3307.94</v>
+        <v>3264</v>
       </c>
       <c r="O12" s="8" t="n">
-        <v>925.01</v>
+        <v>919.995</v>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1" s="42" thickBot="1">

--- a/tasas-transfi.xlsx
+++ b/tasas-transfi.xlsx
@@ -724,8 +724,8 @@
           <t>Conversión del día 💰
 ✅ Dólar paralelo: 68
 Binance
-✅ 1000 Bs = 1.03 = 3364.2 pesos
-✅ 3364.2 pesos = 1.03 = 948.24 Bs
+✅ 1000 Bs = 1.03 = 3395.39 pesos
+✅ 3395.39 pesos = 1.03 = 962.13 Bs
 Promedio competencia
 ✅ Tasa pesos: 20
 ✅ Tasa Bs: 20
@@ -1142,10 +1142,10 @@
         <v/>
       </c>
       <c r="N10" s="8" t="n">
-        <v>972</v>
+        <v>970</v>
       </c>
       <c r="O10" s="8" t="n">
-        <v>3270</v>
+        <v>3293.53</v>
       </c>
     </row>
     <row r="11">
@@ -1178,10 +1178,10 @@
         <v/>
       </c>
       <c r="N12" s="8" t="n">
-        <v>3264</v>
+        <v>3300</v>
       </c>
       <c r="O12" s="8" t="n">
-        <v>919.995</v>
+        <v>935.1</v>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1" s="42" thickBot="1">

--- a/tasas-transfi.xlsx
+++ b/tasas-transfi.xlsx
@@ -724,8 +724,8 @@
           <t>Conversión del día 💰
 ✅ Dólar paralelo: 68
 Binance
-✅ 1000 Bs = 1.03 = 3395.39 pesos
-✅ 3395.39 pesos = 1.03 = 962.13 Bs
+✅ 1000 Bs = 1.02 = 3340.45 pesos
+✅ 3340.45 pesos = 1.01 = 952.68 Bs
 Promedio competencia
 ✅ Tasa pesos: 20
 ✅ Tasa Bs: 20
@@ -1142,10 +1142,10 @@
         <v/>
       </c>
       <c r="N10" s="8" t="n">
-        <v>970</v>
+        <v>984.9880000000001</v>
       </c>
       <c r="O10" s="8" t="n">
-        <v>3293.53</v>
+        <v>3290.3</v>
       </c>
     </row>
     <row r="11">
@@ -1178,10 +1178,10 @@
         <v/>
       </c>
       <c r="N12" s="8" t="n">
-        <v>3300</v>
+        <v>3296</v>
       </c>
       <c r="O12" s="8" t="n">
-        <v>935.1</v>
+        <v>940</v>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1" s="42" thickBot="1">

--- a/tasas-transfi.xlsx
+++ b/tasas-transfi.xlsx
@@ -724,8 +724,8 @@
           <t>Conversión del día 💰
 ✅ Dólar paralelo: 68
 Binance
-✅ 1000 Bs = 1.02 = 3340.45 pesos
-✅ 3340.45 pesos = 1.01 = 952.68 Bs
+✅ 1000 Bs = 1.02 = 3311.97 pesos
+✅ 3311.97 pesos = 1.02 = 964.26 Bs
 Promedio competencia
 ✅ Tasa pesos: 20
 ✅ Tasa Bs: 20
@@ -1142,10 +1142,10 @@
         <v/>
       </c>
       <c r="N10" s="8" t="n">
-        <v>984.9880000000001</v>
+        <v>982.8</v>
       </c>
       <c r="O10" s="8" t="n">
-        <v>3290.3</v>
+        <v>3255</v>
       </c>
     </row>
     <row r="11">
@@ -1178,10 +1178,10 @@
         <v/>
       </c>
       <c r="N12" s="8" t="n">
-        <v>3296</v>
+        <v>3252.68</v>
       </c>
       <c r="O12" s="8" t="n">
-        <v>940</v>
+        <v>947</v>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1" s="42" thickBot="1">

--- a/tasas-transfi.xlsx
+++ b/tasas-transfi.xlsx
@@ -724,8 +724,8 @@
           <t>Conversión del día 💰
 ✅ Dólar paralelo: 68
 Binance
-✅ 1000 Bs = 1.02 = 3311.97 pesos
-✅ 3311.97 pesos = 1.02 = 964.26 Bs
+✅ 1000 Bs = 1.02 = 3289.34 pesos
+✅ 3289.34 pesos = 1.02 = 968.8 Bs
 Promedio competencia
 ✅ Tasa pesos: 20
 ✅ Tasa Bs: 20
@@ -1142,10 +1142,10 @@
         <v/>
       </c>
       <c r="N10" s="8" t="n">
-        <v>982.8</v>
+        <v>985</v>
       </c>
       <c r="O10" s="8" t="n">
-        <v>3255</v>
+        <v>3240</v>
       </c>
     </row>
     <row r="11">
@@ -1178,10 +1178,10 @@
         <v/>
       </c>
       <c r="N12" s="8" t="n">
-        <v>3252.68</v>
+        <v>3225.5</v>
       </c>
       <c r="O12" s="8" t="n">
-        <v>947</v>
+        <v>950</v>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1" s="42" thickBot="1">

--- a/tasas-transfi.xlsx
+++ b/tasas-transfi.xlsx
@@ -724,8 +724,8 @@
           <t>Conversión del día 💰
 ✅ Dólar paralelo: 68
 Binance
-✅ 1000 Bs = 1.02 = 3289.34 pesos
-✅ 3289.34 pesos = 1.02 = 968.8 Bs
+✅ 1000 Bs = 1.02 = 3284.26 pesos
+✅ 3284.26 pesos = 1.01 = 971.09 Bs
 Promedio competencia
 ✅ Tasa pesos: 20
 ✅ Tasa Bs: 20
@@ -1145,7 +1145,7 @@
         <v>985</v>
       </c>
       <c r="O10" s="8" t="n">
-        <v>3240</v>
+        <v>3235</v>
       </c>
     </row>
     <row r="11">
@@ -1178,10 +1178,10 @@
         <v/>
       </c>
       <c r="N12" s="8" t="n">
-        <v>3225.5</v>
+        <v>3240</v>
       </c>
       <c r="O12" s="8" t="n">
-        <v>950</v>
+        <v>958</v>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1" s="42" thickBot="1">

--- a/tasas-transfi.xlsx
+++ b/tasas-transfi.xlsx
@@ -724,8 +724,8 @@
           <t>Conversión del día 💰
 ✅ Dólar paralelo: 68
 Binance
-✅ 1000 Bs = 1.02 = 3284.26 pesos
-✅ 3284.26 pesos = 1.01 = 971.09 Bs
+✅ 1000 Bs = 1.02 = 3284.77 pesos
+✅ 3284.77 pesos = 1.01 = 962.67 Bs
 Promedio competencia
 ✅ Tasa pesos: 20
 ✅ Tasa Bs: 20
@@ -1145,7 +1145,7 @@
         <v>985</v>
       </c>
       <c r="O10" s="8" t="n">
-        <v>3235</v>
+        <v>3235.5</v>
       </c>
     </row>
     <row r="11">
@@ -1178,10 +1178,10 @@
         <v/>
       </c>
       <c r="N12" s="8" t="n">
-        <v>3240</v>
+        <v>3244.99</v>
       </c>
       <c r="O12" s="8" t="n">
-        <v>958</v>
+        <v>951.01</v>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1" s="42" thickBot="1">

--- a/tasas-transfi.xlsx
+++ b/tasas-transfi.xlsx
@@ -724,8 +724,8 @@
           <t>Conversión del día 💰
 ✅ Dólar paralelo: 68
 Binance
-✅ 1000 Bs = 1.02 = 3284.77 pesos
-✅ 3284.77 pesos = 1.01 = 962.67 Bs
+✅ 1000 Bs = 1.02 = 3294.92 pesos
+✅ 3294.92 pesos = 1.01 = 963.5 Bs
 Promedio competencia
 ✅ Tasa pesos: 20
 ✅ Tasa Bs: 20
@@ -1145,7 +1145,7 @@
         <v>985</v>
       </c>
       <c r="O10" s="8" t="n">
-        <v>3235.5</v>
+        <v>3245.5</v>
       </c>
     </row>
     <row r="11">
@@ -1178,10 +1178,10 @@
         <v/>
       </c>
       <c r="N12" s="8" t="n">
-        <v>3244.99</v>
+        <v>3259</v>
       </c>
       <c r="O12" s="8" t="n">
-        <v>951.01</v>
+        <v>953</v>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1" s="42" thickBot="1">

--- a/tasas-transfi.xlsx
+++ b/tasas-transfi.xlsx
@@ -724,8 +724,8 @@
           <t>Conversión del día 💰
 ✅ Dólar paralelo: 68
 Binance
-✅ 1000 Bs = 1.02 = 3294.92 pesos
-✅ 3294.92 pesos = 1.01 = 963.5 Bs
+✅ 1000 Bs = 1.02 = 3310.64 pesos
+✅ 3310.64 pesos = 1.01 = 953.57 Bs
 Promedio competencia
 ✅ Tasa pesos: 20
 ✅ Tasa Bs: 20
@@ -1142,10 +1142,10 @@
         <v/>
       </c>
       <c r="N10" s="8" t="n">
-        <v>985</v>
+        <v>980</v>
       </c>
       <c r="O10" s="8" t="n">
-        <v>3245.5</v>
+        <v>3244.43</v>
       </c>
     </row>
     <row r="11">
@@ -1178,10 +1178,10 @@
         <v/>
       </c>
       <c r="N12" s="8" t="n">
-        <v>3259</v>
+        <v>3267</v>
       </c>
       <c r="O12" s="8" t="n">
-        <v>953</v>
+        <v>941</v>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1" s="42" thickBot="1">

--- a/tasas-transfi.xlsx
+++ b/tasas-transfi.xlsx
@@ -724,8 +724,8 @@
           <t>Conversión del día 💰
 ✅ Dólar paralelo: 68
 Binance
-✅ 1000 Bs = 1.02 = 3310.64 pesos
-✅ 3310.64 pesos = 1.01 = 953.57 Bs
+✅ 1000 Bs = 1.01 = 3227.27 pesos
+✅ 3227.27 pesos = 1.01 = 968.39 Bs
 Promedio competencia
 ✅ Tasa pesos: 20
 ✅ Tasa Bs: 20
@@ -1142,10 +1142,10 @@
         <v/>
       </c>
       <c r="N10" s="8" t="n">
-        <v>980</v>
+        <v>990</v>
       </c>
       <c r="O10" s="8" t="n">
-        <v>3244.43</v>
+        <v>3195</v>
       </c>
     </row>
     <row r="11">
@@ -1178,10 +1178,10 @@
         <v/>
       </c>
       <c r="N12" s="8" t="n">
-        <v>3267</v>
+        <v>3196</v>
       </c>
       <c r="O12" s="8" t="n">
-        <v>941</v>
+        <v>959.01</v>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1" s="42" thickBot="1">

--- a/tasas-transfi.xlsx
+++ b/tasas-transfi.xlsx
@@ -724,8 +724,8 @@
           <t>Conversión del día 💰
 ✅ Dólar paralelo: 68
 Binance
-✅ 1000 Bs = 1.01 = 3227.27 pesos
-✅ 3227.27 pesos = 1.01 = 968.39 Bs
+✅ 1000 Bs = 1.01 = 3222.22 pesos
+✅ 3222.22 pesos = 1.01 = 966.58 Bs
 Promedio competencia
 ✅ Tasa pesos: 20
 ✅ Tasa Bs: 20
@@ -1145,7 +1145,7 @@
         <v>990</v>
       </c>
       <c r="O10" s="8" t="n">
-        <v>3195</v>
+        <v>3190</v>
       </c>
     </row>
     <row r="11">
@@ -1178,7 +1178,7 @@
         <v/>
       </c>
       <c r="N12" s="8" t="n">
-        <v>3196</v>
+        <v>3196.99</v>
       </c>
       <c r="O12" s="8" t="n">
         <v>959.01</v>

--- a/tasas-transfi.xlsx
+++ b/tasas-transfi.xlsx
@@ -724,8 +724,8 @@
           <t>Conversión del día 💰
 ✅ Dólar paralelo: 68
 Binance
-✅ 1000 Bs = 1.01 = 3222.22 pesos
-✅ 3222.22 pesos = 1.01 = 966.58 Bs
+✅ 1000 Bs = 0.98 = 3158.02 pesos
+✅ 3158.02 pesos = 0.98 = 953.43 Bs
 Promedio competencia
 ✅ Tasa pesos: 20
 ✅ Tasa Bs: 20
@@ -1142,10 +1142,10 @@
         <v/>
       </c>
       <c r="N10" s="8" t="n">
-        <v>990</v>
+        <v>1016.999</v>
       </c>
       <c r="O10" s="8" t="n">
-        <v>3190</v>
+        <v>3211.7</v>
       </c>
     </row>
     <row r="11">
@@ -1178,10 +1178,10 @@
         <v/>
       </c>
       <c r="N12" s="8" t="n">
-        <v>3196.99</v>
+        <v>3215</v>
       </c>
       <c r="O12" s="8" t="n">
-        <v>959.01</v>
+        <v>970.6369999999999</v>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1" s="42" thickBot="1">

--- a/tasas-transfi.xlsx
+++ b/tasas-transfi.xlsx
@@ -724,8 +724,8 @@
           <t>Conversión del día 💰
 ✅ Dólar paralelo: 68
 Binance
-✅ 1000 Bs = 0.98 = 3158.02 pesos
-✅ 3158.02 pesos = 0.98 = 953.43 Bs
+✅ 1000 Bs = 0.98 = 3157.36 pesos
+✅ 3157.36 pesos = 0.98 = 947.6 Bs
 Promedio competencia
 ✅ Tasa pesos: 20
 ✅ Tasa Bs: 20
@@ -1145,7 +1145,7 @@
         <v>1016.999</v>
       </c>
       <c r="O10" s="8" t="n">
-        <v>3211.7</v>
+        <v>3211.03</v>
       </c>
     </row>
     <row r="11">
@@ -1178,10 +1178,10 @@
         <v/>
       </c>
       <c r="N12" s="8" t="n">
-        <v>3215</v>
+        <v>3232</v>
       </c>
       <c r="O12" s="8" t="n">
-        <v>970.6369999999999</v>
+        <v>970</v>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1" s="42" thickBot="1">

--- a/tasas-transfi.xlsx
+++ b/tasas-transfi.xlsx
@@ -724,8 +724,8 @@
           <t>Conversión del día 💰
 ✅ Dólar paralelo: 68
 Binance
-✅ 1000 Bs = 0.98 = 3157.36 pesos
-✅ 3157.36 pesos = 0.98 = 947.6 Bs
+✅ 1000 Bs = 0.97 = 3119.43 pesos
+✅ 3119.43 pesos = 0.97 = 956.41 Bs
 Promedio competencia
 ✅ Tasa pesos: 20
 ✅ Tasa Bs: 20
@@ -1142,10 +1142,10 @@
         <v/>
       </c>
       <c r="N10" s="8" t="n">
-        <v>1016.999</v>
+        <v>1030</v>
       </c>
       <c r="O10" s="8" t="n">
-        <v>3211.03</v>
+        <v>3213.01</v>
       </c>
     </row>
     <row r="11">
@@ -1178,10 +1178,10 @@
         <v/>
       </c>
       <c r="N12" s="8" t="n">
-        <v>3232</v>
+        <v>3229</v>
       </c>
       <c r="O12" s="8" t="n">
-        <v>970</v>
+        <v>990</v>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1" s="42" thickBot="1">

--- a/tasas-transfi.xlsx
+++ b/tasas-transfi.xlsx
@@ -724,8 +724,8 @@
           <t>Conversión del día 💰
 ✅ Dólar paralelo: 68
 Binance
-✅ 1000 Bs = 0.97 = 3119.43 pesos
-✅ 3119.43 pesos = 0.97 = 956.41 Bs
+✅ 1000 Bs = 0.98 = 3145.1 pesos
+✅ 3145.1 pesos = 0.98 = 962.17 Bs
 Promedio competencia
 ✅ Tasa pesos: 20
 ✅ Tasa Bs: 20
@@ -1142,10 +1142,10 @@
         <v/>
       </c>
       <c r="N10" s="8" t="n">
-        <v>1030</v>
+        <v>1019.999</v>
       </c>
       <c r="O10" s="8" t="n">
-        <v>3213.01</v>
+        <v>3208</v>
       </c>
     </row>
     <row r="11">
@@ -1178,10 +1178,10 @@
         <v/>
       </c>
       <c r="N12" s="8" t="n">
-        <v>3229</v>
+        <v>3222.98</v>
       </c>
       <c r="O12" s="8" t="n">
-        <v>990</v>
+        <v>986</v>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1" s="42" thickBot="1">

--- a/tasas-transfi.xlsx
+++ b/tasas-transfi.xlsx
@@ -724,8 +724,8 @@
           <t>Conversión del día 💰
 ✅ Dólar paralelo: 68
 Binance
-✅ 1000 Bs = 0.98 = 3145.1 pesos
-✅ 3145.1 pesos = 0.98 = 962.17 Bs
+✅ 1000 Bs = 0.98 = 3132.68 pesos
+✅ 3132.68 pesos = 0.97 = 964.05 Bs
 Promedio competencia
 ✅ Tasa pesos: 20
 ✅ Tasa Bs: 20
@@ -1142,10 +1142,10 @@
         <v/>
       </c>
       <c r="N10" s="8" t="n">
-        <v>1019.999</v>
+        <v>1025</v>
       </c>
       <c r="O10" s="8" t="n">
-        <v>3208</v>
+        <v>3211</v>
       </c>
     </row>
     <row r="11">
@@ -1178,10 +1178,10 @@
         <v/>
       </c>
       <c r="N12" s="8" t="n">
-        <v>3222.98</v>
+        <v>3217</v>
       </c>
       <c r="O12" s="8" t="n">
-        <v>986</v>
+        <v>990</v>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1" s="42" thickBot="1">

--- a/tasas-transfi.xlsx
+++ b/tasas-transfi.xlsx
@@ -724,8 +724,8 @@
           <t>Conversión del día 💰
 ✅ Dólar paralelo: 68
 Binance
-✅ 1000 Bs = 0.98 = 3132.68 pesos
-✅ 3132.68 pesos = 0.97 = 964.05 Bs
+✅ 1000 Bs = 0.97 = 3110.68 pesos
+✅ 3110.68 pesos = 0.97 = 960.33 Bs
 Promedio competencia
 ✅ Tasa pesos: 20
 ✅ Tasa Bs: 20
@@ -1142,10 +1142,10 @@
         <v/>
       </c>
       <c r="N10" s="8" t="n">
-        <v>1025</v>
+        <v>1029.999</v>
       </c>
       <c r="O10" s="8" t="n">
-        <v>3211</v>
+        <v>3204</v>
       </c>
     </row>
     <row r="11">
@@ -1178,10 +1178,10 @@
         <v/>
       </c>
       <c r="N12" s="8" t="n">
-        <v>3217</v>
+        <v>3216.5</v>
       </c>
       <c r="O12" s="8" t="n">
-        <v>990</v>
+        <v>993</v>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1" s="42" thickBot="1">

--- a/tasas-transfi.xlsx
+++ b/tasas-transfi.xlsx
@@ -724,8 +724,8 @@
           <t>Conversión del día 💰
 ✅ Dólar paralelo: 68
 Binance
-✅ 1000 Bs = 0.97 = 3110.68 pesos
-✅ 3110.68 pesos = 0.97 = 960.33 Bs
+✅ 1000 Bs = 0.98 = 3115.74 pesos
+✅ 3115.74 pesos = 0.98 = 958.44 Bs
 Promedio competencia
 ✅ Tasa pesos: 20
 ✅ Tasa Bs: 20
@@ -1142,10 +1142,10 @@
         <v/>
       </c>
       <c r="N10" s="8" t="n">
-        <v>1029.999</v>
+        <v>1019.95</v>
       </c>
       <c r="O10" s="8" t="n">
-        <v>3204</v>
+        <v>3177.9</v>
       </c>
     </row>
     <row r="11">
@@ -1178,10 +1178,10 @@
         <v/>
       </c>
       <c r="N12" s="8" t="n">
-        <v>3216.5</v>
+        <v>3185.84</v>
       </c>
       <c r="O12" s="8" t="n">
-        <v>993</v>
+        <v>980</v>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1" s="42" thickBot="1">

--- a/tasas-transfi.xlsx
+++ b/tasas-transfi.xlsx
@@ -724,8 +724,8 @@
           <t>Conversión del día 💰
 ✅ Dólar paralelo: 68
 Binance
-✅ 1000 Bs = 0.98 = 3115.74 pesos
-✅ 3115.74 pesos = 0.98 = 958.44 Bs
+✅ 1000 Bs = 0.97 = 3086.66 pesos
+✅ 3086.66 pesos = 0.97 = 951.2 Bs
 Promedio competencia
 ✅ Tasa pesos: 20
 ✅ Tasa Bs: 20
@@ -1142,10 +1142,10 @@
         <v/>
       </c>
       <c r="N10" s="8" t="n">
-        <v>1019.95</v>
+        <v>1027</v>
       </c>
       <c r="O10" s="8" t="n">
-        <v>3177.9</v>
+        <v>3170</v>
       </c>
     </row>
     <row r="11">
@@ -1178,7 +1178,7 @@
         <v/>
       </c>
       <c r="N12" s="8" t="n">
-        <v>3185.84</v>
+        <v>3180.1</v>
       </c>
       <c r="O12" s="8" t="n">
         <v>980</v>

--- a/tasas-transfi.xlsx
+++ b/tasas-transfi.xlsx
@@ -724,8 +724,8 @@
           <t>Conversión del día 💰
 ✅ Dólar paralelo: 68
 Binance
-✅ 1000 Bs = 0.97 = 3086.66 pesos
-✅ 3086.66 pesos = 0.97 = 951.2 Bs
+✅ 1000 Bs = 0.97 = 3083.34 pesos
+✅ 3083.34 pesos = 0.97 = 959.24 Bs
 Promedio competencia
 ✅ Tasa pesos: 20
 ✅ Tasa Bs: 20
@@ -1145,7 +1145,7 @@
         <v>1027</v>
       </c>
       <c r="O10" s="8" t="n">
-        <v>3170</v>
+        <v>3166.59</v>
       </c>
     </row>
     <row r="11">
@@ -1178,10 +1178,10 @@
         <v/>
       </c>
       <c r="N12" s="8" t="n">
-        <v>3180.1</v>
+        <v>3179</v>
       </c>
       <c r="O12" s="8" t="n">
-        <v>980</v>
+        <v>989</v>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1" s="42" thickBot="1">

--- a/tasas-transfi.xlsx
+++ b/tasas-transfi.xlsx
@@ -724,8 +724,8 @@
           <t>Conversión del día 💰
 ✅ Dólar paralelo: 68
 Binance
-✅ 1000 Bs = 0.97 = 3083.34 pesos
-✅ 3083.34 pesos = 0.97 = 959.24 Bs
+✅ 1000 Bs = 0.97 = 3094.01 pesos
+✅ 3094.01 pesos = 0.97 = 964.23 Bs
 Promedio competencia
 ✅ Tasa pesos: 20
 ✅ Tasa Bs: 20
@@ -1142,10 +1142,10 @@
         <v/>
       </c>
       <c r="N10" s="8" t="n">
-        <v>1027</v>
+        <v>1026.5</v>
       </c>
       <c r="O10" s="8" t="n">
-        <v>3166.59</v>
+        <v>3176</v>
       </c>
     </row>
     <row r="11">
@@ -1178,10 +1178,10 @@
         <v/>
       </c>
       <c r="N12" s="8" t="n">
-        <v>3179</v>
+        <v>3176.7</v>
       </c>
       <c r="O12" s="8" t="n">
-        <v>989</v>
+        <v>990</v>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1" s="42" thickBot="1">

--- a/tasas-transfi.xlsx
+++ b/tasas-transfi.xlsx
@@ -724,8 +724,8 @@
           <t>Conversión del día 💰
 ✅ Dólar paralelo: 68
 Binance
-✅ 1000 Bs = 0.97 = 3094.01 pesos
-✅ 3094.01 pesos = 0.97 = 964.23 Bs
+✅ 1000 Bs = 0.97 = 3084.47 pesos
+✅ 3084.47 pesos = 0.96 = 952.31 Bs
 Promedio competencia
 ✅ Tasa pesos: 20
 ✅ Tasa Bs: 20
@@ -1142,10 +1142,10 @@
         <v/>
       </c>
       <c r="N10" s="8" t="n">
-        <v>1026.5</v>
+        <v>1030</v>
       </c>
       <c r="O10" s="8" t="n">
-        <v>3176</v>
+        <v>3177</v>
       </c>
     </row>
     <row r="11">
@@ -1178,10 +1178,10 @@
         <v/>
       </c>
       <c r="N12" s="8" t="n">
-        <v>3176.7</v>
+        <v>3199.09</v>
       </c>
       <c r="O12" s="8" t="n">
-        <v>990</v>
+        <v>987.7</v>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1" s="42" thickBot="1">

--- a/tasas-transfi.xlsx
+++ b/tasas-transfi.xlsx
@@ -724,8 +724,8 @@
           <t>Conversión del día 💰
 ✅ Dólar paralelo: 68
 Binance
-✅ 1000 Bs = 0.97 = 3084.47 pesos
-✅ 3084.47 pesos = 0.96 = 952.31 Bs
+✅ 1000 Bs = 0.97 = 3082.52 pesos
+✅ 3082.52 pesos = 0.96 = 943.95 Bs
 Promedio competencia
 ✅ Tasa pesos: 20
 ✅ Tasa Bs: 20
@@ -1145,7 +1145,7 @@
         <v>1030</v>
       </c>
       <c r="O10" s="8" t="n">
-        <v>3177</v>
+        <v>3175</v>
       </c>
     </row>
     <row r="11">
@@ -1178,10 +1178,10 @@
         <v/>
       </c>
       <c r="N12" s="8" t="n">
-        <v>3199.09</v>
+        <v>3197</v>
       </c>
       <c r="O12" s="8" t="n">
-        <v>987.7</v>
+        <v>979.01</v>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1" s="42" thickBot="1">

--- a/tasas-transfi.xlsx
+++ b/tasas-transfi.xlsx
@@ -724,8 +724,8 @@
           <t>Conversión del día 💰
 ✅ Dólar paralelo: 68
 Binance
-✅ 1000 Bs = 0.97 = 3082.52 pesos
-✅ 3082.52 pesos = 0.96 = 943.95 Bs
+✅ 1000 Bs = 0.98 = 3105.47 pesos
+✅ 3105.47 pesos = 0.97 = 953.59 Bs
 Promedio competencia
 ✅ Tasa pesos: 20
 ✅ Tasa Bs: 20
@@ -1142,10 +1142,10 @@
         <v/>
       </c>
       <c r="N10" s="8" t="n">
-        <v>1030</v>
+        <v>1024</v>
       </c>
       <c r="O10" s="8" t="n">
-        <v>3175</v>
+        <v>3180</v>
       </c>
     </row>
     <row r="11">
@@ -1178,10 +1178,10 @@
         <v/>
       </c>
       <c r="N12" s="8" t="n">
-        <v>3197</v>
+        <v>3189.99</v>
       </c>
       <c r="O12" s="8" t="n">
-        <v>979.01</v>
+        <v>979.545</v>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1" s="42" thickBot="1">

--- a/tasas-transfi.xlsx
+++ b/tasas-transfi.xlsx
@@ -725,7 +725,7 @@
 ✅ Dólar paralelo: 68
 Binance
 ✅ 1000 Bs = 0.98 = 3105.47 pesos
-✅ 3105.47 pesos = 0.97 = 953.59 Bs
+✅ 3105.47 pesos = 0.98 = 955.11 Bs
 Promedio competencia
 ✅ Tasa pesos: 20
 ✅ Tasa Bs: 20
@@ -1178,10 +1178,10 @@
         <v/>
       </c>
       <c r="N12" s="8" t="n">
-        <v>3189.99</v>
+        <v>3185</v>
       </c>
       <c r="O12" s="8" t="n">
-        <v>979.545</v>
+        <v>979.574</v>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1" s="42" thickBot="1">

--- a/tasas-transfi.xlsx
+++ b/tasas-transfi.xlsx
@@ -724,8 +724,8 @@
           <t>Conversión del día 💰
 ✅ Dólar paralelo: 68
 Binance
-✅ 1000 Bs = 0.98 = 3105.47 pesos
-✅ 3105.47 pesos = 0.98 = 955.11 Bs
+✅ 1000 Bs = 0.98 = 3085.94 pesos
+✅ 3085.94 pesos = 0.97 = 959.99 Bs
 Promedio competencia
 ✅ Tasa pesos: 20
 ✅ Tasa Bs: 20
@@ -1145,7 +1145,7 @@
         <v>1024</v>
       </c>
       <c r="O10" s="8" t="n">
-        <v>3180</v>
+        <v>3160</v>
       </c>
     </row>
     <row r="11">
@@ -1178,10 +1178,10 @@
         <v/>
       </c>
       <c r="N12" s="8" t="n">
-        <v>3185</v>
+        <v>3175</v>
       </c>
       <c r="O12" s="8" t="n">
-        <v>979.574</v>
+        <v>987.7</v>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1" s="42" thickBot="1">

--- a/tasas-transfi.xlsx
+++ b/tasas-transfi.xlsx
@@ -724,8 +724,8 @@
           <t>Conversión del día 💰
 ✅ Dólar paralelo: 68
 Binance
-✅ 1000 Bs = 0.98 = 3085.94 pesos
-✅ 3085.94 pesos = 0.97 = 959.99 Bs
+✅ 1000 Bs = 0.98 = 3090.82 pesos
+✅ 3090.82 pesos = 0.97 = 954.12 Bs
 Promedio competencia
 ✅ Tasa pesos: 20
 ✅ Tasa Bs: 20
@@ -1145,7 +1145,7 @@
         <v>1024</v>
       </c>
       <c r="O10" s="8" t="n">
-        <v>3160</v>
+        <v>3165</v>
       </c>
     </row>
     <row r="11">
@@ -1181,7 +1181,7 @@
         <v>3175</v>
       </c>
       <c r="O12" s="8" t="n">
-        <v>987.7</v>
+        <v>980.11</v>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1" s="42" thickBot="1">

--- a/tasas-transfi.xlsx
+++ b/tasas-transfi.xlsx
@@ -724,8 +724,8 @@
           <t>Conversión del día 💰
 ✅ Dólar paralelo: 68
 Binance
-✅ 1000 Bs = 0.98 = 3090.82 pesos
-✅ 3090.82 pesos = 0.97 = 954.12 Bs
+✅ 1000 Bs = 0.98 = 3101.56 pesos
+✅ 3101.56 pesos = 0.97 = 952.98 Bs
 Promedio competencia
 ✅ Tasa pesos: 20
 ✅ Tasa Bs: 20
@@ -1145,7 +1145,7 @@
         <v>1024</v>
       </c>
       <c r="O10" s="8" t="n">
-        <v>3165</v>
+        <v>3176</v>
       </c>
     </row>
     <row r="11">
@@ -1178,10 +1178,10 @@
         <v/>
       </c>
       <c r="N12" s="8" t="n">
-        <v>3175</v>
+        <v>3183</v>
       </c>
       <c r="O12" s="8" t="n">
-        <v>980.11</v>
+        <v>978.001</v>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1" s="42" thickBot="1">

--- a/tasas-transfi.xlsx
+++ b/tasas-transfi.xlsx
@@ -724,8 +724,8 @@
           <t>Conversión del día 💰
 ✅ Dólar paralelo: 68
 Binance
-✅ 1000 Bs = 0.98 = 3101.56 pesos
-✅ 3101.56 pesos = 0.97 = 952.98 Bs
+✅ 1000 Bs = 0.98 = 3104.02 pesos
+✅ 3104.02 pesos = 0.98 = 962.64 Bs
 Promedio competencia
 ✅ Tasa pesos: 20
 ✅ Tasa Bs: 20
@@ -1142,10 +1142,10 @@
         <v/>
       </c>
       <c r="N10" s="8" t="n">
-        <v>1024</v>
+        <v>1019</v>
       </c>
       <c r="O10" s="8" t="n">
-        <v>3176</v>
+        <v>3163</v>
       </c>
     </row>
     <row r="11">
@@ -1178,10 +1178,10 @@
         <v/>
       </c>
       <c r="N12" s="8" t="n">
-        <v>3183</v>
+        <v>3179</v>
       </c>
       <c r="O12" s="8" t="n">
-        <v>978.001</v>
+        <v>985.888</v>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1" s="42" thickBot="1">

--- a/tasas-transfi.xlsx
+++ b/tasas-transfi.xlsx
@@ -724,8 +724,8 @@
           <t>Conversión del día 💰
 ✅ Dólar paralelo: 68
 Binance
-✅ 1000 Bs = 0.98 = 3104.02 pesos
-✅ 3104.02 pesos = 0.98 = 962.64 Bs
+✅ 1000 Bs = 0.98 = 3092.58 pesos
+✅ 3092.58 pesos = 0.97 = 961.21 Bs
 Promedio competencia
 ✅ Tasa pesos: 20
 ✅ Tasa Bs: 20
@@ -1142,10 +1142,10 @@
         <v/>
       </c>
       <c r="N10" s="8" t="n">
-        <v>1019</v>
+        <v>1021.8</v>
       </c>
       <c r="O10" s="8" t="n">
-        <v>3163</v>
+        <v>3160</v>
       </c>
     </row>
     <row r="11">
@@ -1178,7 +1178,7 @@
         <v/>
       </c>
       <c r="N12" s="8" t="n">
-        <v>3179</v>
+        <v>3171.99</v>
       </c>
       <c r="O12" s="8" t="n">
         <v>985.888</v>

--- a/tasas-transfi.xlsx
+++ b/tasas-transfi.xlsx
@@ -724,8 +724,8 @@
           <t>Conversión del día 💰
 ✅ Dólar paralelo: 68
 Binance
-✅ 1000 Bs = 0.98 = 3092.58 pesos
-✅ 3092.58 pesos = 0.97 = 961.21 Bs
+✅ 1000 Bs = 0.98 = 3097.48 pesos
+✅ 3097.48 pesos = 0.98 = 955.41 Bs
 Promedio competencia
 ✅ Tasa pesos: 20
 ✅ Tasa Bs: 20
@@ -1145,7 +1145,7 @@
         <v>1021.8</v>
       </c>
       <c r="O10" s="8" t="n">
-        <v>3160</v>
+        <v>3165</v>
       </c>
     </row>
     <row r="11">
@@ -1178,10 +1178,10 @@
         <v/>
       </c>
       <c r="N12" s="8" t="n">
-        <v>3171.99</v>
+        <v>3170</v>
       </c>
       <c r="O12" s="8" t="n">
-        <v>985.888</v>
+        <v>977.777</v>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1" s="42" thickBot="1">

--- a/tasas-transfi.xlsx
+++ b/tasas-transfi.xlsx
@@ -724,8 +724,8 @@
           <t>Conversión del día 💰
 ✅ Dólar paralelo: 68
 Binance
-✅ 1000 Bs = 0.98 = 3097.48 pesos
-✅ 3097.48 pesos = 0.98 = 955.41 Bs
+✅ 1000 Bs = 0.99 = 3117.79 pesos
+✅ 3117.79 pesos = 0.98 = 942.91 Bs
 Promedio competencia
 ✅ Tasa pesos: 20
 ✅ Tasa Bs: 20
@@ -1142,10 +1142,10 @@
         <v/>
       </c>
       <c r="N10" s="8" t="n">
-        <v>1021.8</v>
+        <v>1011.999</v>
       </c>
       <c r="O10" s="8" t="n">
-        <v>3165</v>
+        <v>3155.2</v>
       </c>
     </row>
     <row r="11">
@@ -1178,10 +1178,10 @@
         <v/>
       </c>
       <c r="N12" s="8" t="n">
-        <v>3170</v>
+        <v>3171</v>
       </c>
       <c r="O12" s="8" t="n">
-        <v>977.777</v>
+        <v>959.0069999999999</v>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1" s="42" thickBot="1">

--- a/tasas-transfi.xlsx
+++ b/tasas-transfi.xlsx
@@ -724,8 +724,8 @@
           <t>Conversión del día 💰
 ✅ Dólar paralelo: 68
 Binance
-✅ 1000 Bs = 0.99 = 3117.79 pesos
-✅ 3117.79 pesos = 0.98 = 942.91 Bs
+✅ 1000 Bs = 0.98 = 3107.17 pesos
+✅ 3107.17 pesos = 0.98 = 941.03 Bs
 Promedio competencia
 ✅ Tasa pesos: 20
 ✅ Tasa Bs: 20
@@ -1142,10 +1142,10 @@
         <v/>
       </c>
       <c r="N10" s="8" t="n">
-        <v>1011.999</v>
+        <v>1017</v>
       </c>
       <c r="O10" s="8" t="n">
-        <v>3155.2</v>
+        <v>3159.99</v>
       </c>
     </row>
     <row r="11">
@@ -1178,10 +1178,10 @@
         <v/>
       </c>
       <c r="N12" s="8" t="n">
-        <v>3171</v>
+        <v>3176.4</v>
       </c>
       <c r="O12" s="8" t="n">
-        <v>959.0069999999999</v>
+        <v>962</v>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1" s="42" thickBot="1">

--- a/tasas-transfi.xlsx
+++ b/tasas-transfi.xlsx
@@ -724,8 +724,8 @@
           <t>Conversión del día 💰
 ✅ Dólar paralelo: 68
 Binance
-✅ 1000 Bs = 0.98 = 3107.17 pesos
-✅ 3107.17 pesos = 0.98 = 941.03 Bs
+✅ 1000 Bs = 0.98 = 3095.34 pesos
+✅ 3095.34 pesos = 0.98 = 960.14 Bs
 Promedio competencia
 ✅ Tasa pesos: 20
 ✅ Tasa Bs: 20
@@ -1142,10 +1142,10 @@
         <v/>
       </c>
       <c r="N10" s="8" t="n">
-        <v>1017</v>
+        <v>1020.89</v>
       </c>
       <c r="O10" s="8" t="n">
-        <v>3159.99</v>
+        <v>3160</v>
       </c>
     </row>
     <row r="11">
@@ -1178,10 +1178,10 @@
         <v/>
       </c>
       <c r="N12" s="8" t="n">
-        <v>3176.4</v>
+        <v>3160</v>
       </c>
       <c r="O12" s="8" t="n">
-        <v>962</v>
+        <v>980.2</v>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1" s="42" thickBot="1">

--- a/tasas-transfi.xlsx
+++ b/tasas-transfi.xlsx
@@ -724,8 +724,8 @@
           <t>Conversión del día 💰
 ✅ Dólar paralelo: 68
 Binance
-✅ 1000 Bs = 0.98 = 3095.34 pesos
-✅ 3095.34 pesos = 0.98 = 960.14 Bs
+✅ 1000 Bs = 0.99 = 3103.45 pesos
+✅ 3103.45 pesos = 0.98 = 955.14 Bs
 Promedio competencia
 ✅ Tasa pesos: 20
 ✅ Tasa Bs: 20
@@ -1142,10 +1142,10 @@
         <v/>
       </c>
       <c r="N10" s="8" t="n">
-        <v>1020.89</v>
+        <v>1014.999</v>
       </c>
       <c r="O10" s="8" t="n">
-        <v>3160</v>
+        <v>3150</v>
       </c>
     </row>
     <row r="11">
@@ -1178,10 +1178,10 @@
         <v/>
       </c>
       <c r="N12" s="8" t="n">
-        <v>3160</v>
+        <v>3167.99</v>
       </c>
       <c r="O12" s="8" t="n">
-        <v>980.2</v>
+        <v>975</v>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1" s="42" thickBot="1">

--- a/tasas-transfi.xlsx
+++ b/tasas-transfi.xlsx
@@ -724,8 +724,8 @@
           <t>Conversión del día 💰
 ✅ Dólar paralelo: 68
 Binance
-✅ 1000 Bs = 0.99 = 3103.45 pesos
-✅ 3103.45 pesos = 0.98 = 955.14 Bs
+✅ 1000 Bs = 0.98 = 3081.72 pesos
+✅ 3081.72 pesos = 0.97 = 946.21 Bs
 Promedio competencia
 ✅ Tasa pesos: 20
 ✅ Tasa Bs: 20
@@ -1142,10 +1142,10 @@
         <v/>
       </c>
       <c r="N10" s="8" t="n">
-        <v>1014.999</v>
+        <v>1023</v>
       </c>
       <c r="O10" s="8" t="n">
-        <v>3150</v>
+        <v>3152.6</v>
       </c>
     </row>
     <row r="11">
@@ -1178,7 +1178,7 @@
         <v/>
       </c>
       <c r="N12" s="8" t="n">
-        <v>3167.99</v>
+        <v>3175.5</v>
       </c>
       <c r="O12" s="8" t="n">
         <v>975</v>

--- a/tasas-transfi.xlsx
+++ b/tasas-transfi.xlsx
@@ -724,8 +724,8 @@
           <t>Conversión del día 💰
 ✅ Dólar paralelo: 68
 Binance
-✅ 1000 Bs = 0.98 = 3081.72 pesos
-✅ 3081.72 pesos = 0.97 = 946.21 Bs
+✅ 1000 Bs = 0.99 = 3111.33 pesos
+✅ 3111.33 pesos = 0.98 = 951.18 Bs
 Promedio competencia
 ✅ Tasa pesos: 20
 ✅ Tasa Bs: 20
@@ -1142,10 +1142,10 @@
         <v/>
       </c>
       <c r="N10" s="8" t="n">
-        <v>1023</v>
+        <v>1015</v>
       </c>
       <c r="O10" s="8" t="n">
-        <v>3152.6</v>
+        <v>3158</v>
       </c>
     </row>
     <row r="11">
@@ -1178,10 +1178,10 @@
         <v/>
       </c>
       <c r="N12" s="8" t="n">
-        <v>3175.5</v>
+        <v>3172.87</v>
       </c>
       <c r="O12" s="8" t="n">
-        <v>975</v>
+        <v>969.995</v>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1" s="42" thickBot="1">

--- a/tasas-transfi.xlsx
+++ b/tasas-transfi.xlsx
@@ -724,8 +724,8 @@
           <t>Conversión del día 💰
 ✅ Dólar paralelo: 68
 Binance
-✅ 1000 Bs = 0.99 = 3111.33 pesos
-✅ 3111.33 pesos = 0.98 = 951.18 Bs
+✅ 1000 Bs = 0.98 = 3076.96 pesos
+✅ 3076.96 pesos = 0.97 = 954.29 Bs
 Promedio competencia
 ✅ Tasa pesos: 20
 ✅ Tasa Bs: 20
@@ -1142,10 +1142,10 @@
         <v/>
       </c>
       <c r="N10" s="8" t="n">
-        <v>1015</v>
+        <v>1019.999</v>
       </c>
       <c r="O10" s="8" t="n">
-        <v>3158</v>
+        <v>3138.5</v>
       </c>
     </row>
     <row r="11">
@@ -1178,10 +1178,10 @@
         <v/>
       </c>
       <c r="N12" s="8" t="n">
-        <v>3172.87</v>
+        <v>3159.85</v>
       </c>
       <c r="O12" s="8" t="n">
-        <v>969.995</v>
+        <v>980</v>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1" s="42" thickBot="1">

--- a/tasas-transfi.xlsx
+++ b/tasas-transfi.xlsx
@@ -724,8 +724,8 @@
           <t>Conversión del día 💰
 ✅ Dólar paralelo: 68
 Binance
-✅ 1000 Bs = 0.98 = 3076.96 pesos
-✅ 3076.96 pesos = 0.97 = 954.29 Bs
+✅ 1000 Bs = 0.99 = 3090.64 pesos
+✅ 3090.64 pesos = 0.98 = 961.69 Bs
 Promedio competencia
 ✅ Tasa pesos: 20
 ✅ Tasa Bs: 20
@@ -1142,10 +1142,10 @@
         <v/>
       </c>
       <c r="N10" s="8" t="n">
-        <v>1019.999</v>
+        <v>1014.999</v>
       </c>
       <c r="O10" s="8" t="n">
-        <v>3138.5</v>
+        <v>3137</v>
       </c>
     </row>
     <row r="11">
@@ -1178,7 +1178,7 @@
         <v/>
       </c>
       <c r="N12" s="8" t="n">
-        <v>3159.85</v>
+        <v>3149.5</v>
       </c>
       <c r="O12" s="8" t="n">
         <v>980</v>

--- a/tasas-transfi.xlsx
+++ b/tasas-transfi.xlsx
@@ -724,8 +724,8 @@
           <t>Conversión del día 💰
 ✅ Dólar paralelo: 68
 Binance
-✅ 1000 Bs = 0.99 = 3090.64 pesos
-✅ 3090.64 pesos = 0.98 = 961.69 Bs
+✅ 1000 Bs = 0.99 = 3108.36 pesos
+✅ 3108.36 pesos = 0.98 = 954.38 Bs
 Promedio competencia
 ✅ Tasa pesos: 20
 ✅ Tasa Bs: 20
@@ -1142,10 +1142,10 @@
         <v/>
       </c>
       <c r="N10" s="8" t="n">
-        <v>1014.999</v>
+        <v>1012.148</v>
       </c>
       <c r="O10" s="8" t="n">
-        <v>3137</v>
+        <v>3146.12</v>
       </c>
     </row>
     <row r="11">
@@ -1178,10 +1178,10 @@
         <v/>
       </c>
       <c r="N12" s="8" t="n">
-        <v>3149.5</v>
+        <v>3169</v>
       </c>
       <c r="O12" s="8" t="n">
-        <v>980</v>
+        <v>973.002</v>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1" s="42" thickBot="1">

--- a/tasas-transfi.xlsx
+++ b/tasas-transfi.xlsx
@@ -724,8 +724,8 @@
           <t>Conversión del día 💰
 ✅ Dólar paralelo: 68
 Binance
-✅ 1000 Bs = 0.99 = 3108.36 pesos
-✅ 3108.36 pesos = 0.98 = 954.38 Bs
+✅ 1000 Bs = 0.98 = 3095.1 pesos
+✅ 3095.1 pesos = 0.98 = 960.48 Bs
 Promedio competencia
 ✅ Tasa pesos: 20
 ✅ Tasa Bs: 20
@@ -1142,10 +1142,10 @@
         <v/>
       </c>
       <c r="N10" s="8" t="n">
-        <v>1012.148</v>
+        <v>1015.8</v>
       </c>
       <c r="O10" s="8" t="n">
-        <v>3146.12</v>
+        <v>3144</v>
       </c>
     </row>
     <row r="11">
@@ -1178,10 +1178,10 @@
         <v/>
       </c>
       <c r="N12" s="8" t="n">
-        <v>3169</v>
+        <v>3158</v>
       </c>
       <c r="O12" s="8" t="n">
-        <v>973.002</v>
+        <v>980</v>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1" s="42" thickBot="1">

--- a/tasas-transfi.xlsx
+++ b/tasas-transfi.xlsx
@@ -724,8 +724,8 @@
           <t>Conversión del día 💰
 ✅ Dólar paralelo: 68
 Binance
-✅ 1000 Bs = 0.98 = 3095.1 pesos
-✅ 3095.1 pesos = 0.98 = 960.48 Bs
+✅ 1000 Bs = 0.99 = 3121.51 pesos
+✅ 3121.51 pesos = 0.99 = 965.92 Bs
 Promedio competencia
 ✅ Tasa pesos: 20
 ✅ Tasa Bs: 20
@@ -1142,10 +1142,10 @@
         <v/>
       </c>
       <c r="N10" s="8" t="n">
-        <v>1015.8</v>
+        <v>1015</v>
       </c>
       <c r="O10" s="8" t="n">
-        <v>3144</v>
+        <v>3168.33</v>
       </c>
     </row>
     <row r="11">
@@ -1178,7 +1178,7 @@
         <v/>
       </c>
       <c r="N12" s="8" t="n">
-        <v>3158</v>
+        <v>3167</v>
       </c>
       <c r="O12" s="8" t="n">
         <v>980</v>

--- a/tasas-transfi.xlsx
+++ b/tasas-transfi.xlsx
@@ -724,8 +724,8 @@
           <t>Conversión del día 💰
 ✅ Dólar paralelo: 68
 Binance
-✅ 1000 Bs = 0.99 = 3121.51 pesos
-✅ 3121.51 pesos = 0.99 = 965.92 Bs
+✅ 1000 Bs = 0.99 = 3119.71 pesos
+✅ 3119.71 pesos = 0.98 = 962.97 Bs
 Promedio competencia
 ✅ Tasa pesos: 20
 ✅ Tasa Bs: 20
@@ -1142,10 +1142,10 @@
         <v/>
       </c>
       <c r="N10" s="8" t="n">
-        <v>1015</v>
+        <v>1014.999</v>
       </c>
       <c r="O10" s="8" t="n">
-        <v>3168.33</v>
+        <v>3166.5</v>
       </c>
     </row>
     <row r="11">
@@ -1178,7 +1178,7 @@
         <v/>
       </c>
       <c r="N12" s="8" t="n">
-        <v>3167</v>
+        <v>3174.89</v>
       </c>
       <c r="O12" s="8" t="n">
         <v>980</v>
